--- a/public/TagThieuKet.xlsx
+++ b/public/TagThieuKet.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3BF108-DF94-4CCA-83BF-FA5E16AE8CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC212CF6-2510-41E0-BCF7-EA4981839AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="3540" yWindow="3540" windowWidth="21600" windowHeight="11385" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="TK1" sheetId="6" r:id="rId1"/>
-    <sheet name="TK2" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="155">
   <si>
     <t>Tag0</t>
   </si>
@@ -454,18 +453,6 @@
     <t>Tag52</t>
   </si>
   <si>
-    <t>Ống gió chính # 3</t>
-  </si>
-  <si>
-    <t>Ống gió chính # 4</t>
-  </si>
-  <si>
-    <t>Độ mở quạt gió #3</t>
-  </si>
-  <si>
-    <t>Độ mở quạt gió #4</t>
-  </si>
-  <si>
     <t>Độ dày lớp liệu</t>
   </si>
   <si>
@@ -497,168 +484,6 @@
   </si>
   <si>
     <t>Tag57</t>
-  </si>
-  <si>
-    <t>2YG_Frequency_VFD</t>
-  </si>
-  <si>
-    <t>2SJ_Frequency_VFD</t>
-  </si>
-  <si>
-    <t>TI641aBM</t>
-  </si>
-  <si>
-    <t>3_Blower_inlet_valve_location_1</t>
-  </si>
-  <si>
-    <t>4_Blower_inlet_valve_location_1</t>
-  </si>
-  <si>
-    <t>TI601aBM</t>
-  </si>
-  <si>
-    <t>PI601aBM</t>
-  </si>
-  <si>
-    <t>TI601bBM</t>
-  </si>
-  <si>
-    <t>PI601bBM</t>
-  </si>
-  <si>
-    <t>TI602aBM</t>
-  </si>
-  <si>
-    <t>PI602aBM</t>
-  </si>
-  <si>
-    <t>TI602bBM</t>
-  </si>
-  <si>
-    <t>PI602bBM</t>
-  </si>
-  <si>
-    <t>TI603aBM</t>
-  </si>
-  <si>
-    <t>PI603aBM</t>
-  </si>
-  <si>
-    <t>TI603bBM</t>
-  </si>
-  <si>
-    <t>PI603bBM</t>
-  </si>
-  <si>
-    <t>TI614aBM</t>
-  </si>
-  <si>
-    <t>PI614aBM</t>
-  </si>
-  <si>
-    <t>TI614bBM</t>
-  </si>
-  <si>
-    <t>PI614bBM</t>
-  </si>
-  <si>
-    <t>TI615aBM</t>
-  </si>
-  <si>
-    <t>PI615aBM</t>
-  </si>
-  <si>
-    <t>TI615bBM</t>
-  </si>
-  <si>
-    <t>PI615bBM</t>
-  </si>
-  <si>
-    <t>TI616aBM</t>
-  </si>
-  <si>
-    <t>PI616aBM</t>
-  </si>
-  <si>
-    <t>TI616bBM</t>
-  </si>
-  <si>
-    <t>PI616bBM</t>
-  </si>
-  <si>
-    <t>TI617aBM</t>
-  </si>
-  <si>
-    <t>PI617aBM</t>
-  </si>
-  <si>
-    <t>TI617bBM</t>
-  </si>
-  <si>
-    <t>PI617bBM</t>
-  </si>
-  <si>
-    <t>TI618aBM</t>
-  </si>
-  <si>
-    <t>PI618aBM</t>
-  </si>
-  <si>
-    <t>TI618bBM</t>
-  </si>
-  <si>
-    <t>PI618bBM</t>
-  </si>
-  <si>
-    <t>TI619aBM</t>
-  </si>
-  <si>
-    <t>PI619aBM</t>
-  </si>
-  <si>
-    <t>TI619bBM</t>
-  </si>
-  <si>
-    <t>PI619bBM</t>
-  </si>
-  <si>
-    <t>TI620aBM</t>
-  </si>
-  <si>
-    <t>PI620aBM</t>
-  </si>
-  <si>
-    <t>TI620bBM</t>
-  </si>
-  <si>
-    <t>PI620bBM</t>
-  </si>
-  <si>
-    <t>TI621aBM</t>
-  </si>
-  <si>
-    <t>PI621aBM</t>
-  </si>
-  <si>
-    <t>TI621bBM</t>
-  </si>
-  <si>
-    <t>PI621bBM</t>
-  </si>
-  <si>
-    <t>TI636bBM</t>
-  </si>
-  <si>
-    <t>PI801bBM</t>
-  </si>
-  <si>
-    <t>TI636aBM</t>
-  </si>
-  <si>
-    <t>PI801aBM</t>
-  </si>
-  <si>
-    <t>LI601eBM</t>
   </si>
   <si>
     <t>LI601aAM</t>
@@ -804,9 +629,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -814,6 +636,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1183,7 +1008,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1197,7 +1022,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
@@ -1209,7 +1034,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1223,7 +1048,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1235,7 +1060,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
@@ -1247,7 +1072,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="1" t="s">
         <v>41</v>
       </c>
@@ -1259,7 +1084,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
+      <c r="A10" s="5"/>
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1271,7 +1096,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
+      <c r="A11" s="5"/>
       <c r="B11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1283,7 +1108,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
+      <c r="A12" s="5"/>
       <c r="B12" s="1" t="s">
         <v>44</v>
       </c>
@@ -1295,7 +1120,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="1" t="s">
         <v>45</v>
       </c>
@@ -1307,7 +1132,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
+      <c r="A14" s="5"/>
       <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
@@ -1319,7 +1144,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="1" t="s">
         <v>47</v>
       </c>
@@ -1331,7 +1156,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="1" t="s">
         <v>48</v>
       </c>
@@ -1343,7 +1168,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1355,7 +1180,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
+      <c r="A18" s="5"/>
       <c r="B18" s="1" t="s">
         <v>50</v>
       </c>
@@ -1367,7 +1192,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
+      <c r="A19" s="5"/>
       <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1379,7 +1204,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+      <c r="A20" s="5"/>
       <c r="B20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1391,7 +1216,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
+      <c r="A21" s="5"/>
       <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
@@ -1403,7 +1228,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
+      <c r="A22" s="5"/>
       <c r="B22" s="1" t="s">
         <v>54</v>
       </c>
@@ -1415,7 +1240,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
+      <c r="A23" s="5"/>
       <c r="B23" s="1" t="s">
         <v>55</v>
       </c>
@@ -1427,7 +1252,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
+      <c r="A24" s="5"/>
       <c r="B24" s="1" t="s">
         <v>56</v>
       </c>
@@ -1439,7 +1264,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
+      <c r="A25" s="5"/>
       <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
@@ -1451,7 +1276,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
+      <c r="A26" s="5"/>
       <c r="B26" s="1" t="s">
         <v>58</v>
       </c>
@@ -1463,7 +1288,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
+      <c r="A27" s="5"/>
       <c r="B27" s="1" t="s">
         <v>59</v>
       </c>
@@ -1475,7 +1300,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
+      <c r="A28" s="5"/>
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
@@ -1487,7 +1312,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
+      <c r="A29" s="6"/>
       <c r="B29" s="1" t="s">
         <v>119</v>
       </c>
@@ -1499,7 +1324,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1513,7 +1338,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
+      <c r="A31" s="7"/>
       <c r="B31" s="1" t="s">
         <v>39</v>
       </c>
@@ -1525,7 +1350,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
+      <c r="A32" s="7"/>
       <c r="B32" s="1" t="s">
         <v>40</v>
       </c>
@@ -1537,7 +1362,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
+      <c r="A33" s="7"/>
       <c r="B33" s="1" t="s">
         <v>41</v>
       </c>
@@ -1549,7 +1374,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
+      <c r="A34" s="7"/>
       <c r="B34" s="1" t="s">
         <v>42</v>
       </c>
@@ -1561,7 +1386,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
+      <c r="A35" s="7"/>
       <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
@@ -1573,7 +1398,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
+      <c r="A36" s="7"/>
       <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
@@ -1585,7 +1410,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="1" t="s">
         <v>45</v>
       </c>
@@ -1597,7 +1422,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
+      <c r="A38" s="7"/>
       <c r="B38" s="1" t="s">
         <v>46</v>
       </c>
@@ -1609,7 +1434,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="1" t="s">
         <v>47</v>
       </c>
@@ -1621,7 +1446,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="1" t="s">
         <v>48</v>
       </c>
@@ -1633,7 +1458,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
@@ -1645,7 +1470,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="1" t="s">
         <v>50</v>
       </c>
@@ -1657,7 +1482,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="1" t="s">
         <v>51</v>
       </c>
@@ -1669,7 +1494,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="7"/>
       <c r="B44" s="1" t="s">
         <v>52</v>
       </c>
@@ -1681,7 +1506,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
+      <c r="A45" s="7"/>
       <c r="B45" s="1" t="s">
         <v>53</v>
       </c>
@@ -1693,7 +1518,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="7"/>
       <c r="B46" s="1" t="s">
         <v>54</v>
       </c>
@@ -1705,7 +1530,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="1" t="s">
         <v>55</v>
       </c>
@@ -1717,7 +1542,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
+      <c r="A48" s="7"/>
       <c r="B48" s="1" t="s">
         <v>56</v>
       </c>
@@ -1729,7 +1554,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="7"/>
       <c r="B49" s="1" t="s">
         <v>57</v>
       </c>
@@ -1741,7 +1566,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="7"/>
       <c r="B50" s="1" t="s">
         <v>58</v>
       </c>
@@ -1753,7 +1578,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="1" t="s">
         <v>59</v>
       </c>
@@ -1765,7 +1590,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="7"/>
       <c r="B52" s="1" t="s">
         <v>118</v>
       </c>
@@ -1777,7 +1602,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
+      <c r="A53" s="7"/>
       <c r="B53" s="1" t="s">
         <v>119</v>
       </c>
@@ -1789,65 +1614,65 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="5"/>
+      <c r="B55" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="5"/>
+      <c r="B56" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="5"/>
+      <c r="B57" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="6"/>
-      <c r="B55" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="6"/>
-      <c r="B56" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="6"/>
-      <c r="B57" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
-      <c r="B58" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="D58" s="1" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1863,734 +1688,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7D2511-DCAF-44B1-9A55-9E3C72837790}">
-  <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="B49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="6"/>
-      <c r="B55" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="6"/>
-      <c r="B56" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="6"/>
-      <c r="B57" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
-      <c r="B58" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A29"/>
-    <mergeCell ref="A30:A53"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/public/TagThieuKet.xlsx
+++ b/public/TagThieuKet.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC212CF6-2510-41E0-BCF7-EA4981839AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C091E6-7ADB-4214-9C2A-9C38FD540F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="3540" windowWidth="21600" windowHeight="11385" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="TK1" sheetId="6" r:id="rId1"/>
+    <sheet name="TK2" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="213">
   <si>
     <t>Tag0</t>
   </si>
@@ -499,6 +500,180 @@
   </si>
   <si>
     <t>LI601eAM</t>
+  </si>
+  <si>
+    <t>2YG_Frequency_VFD</t>
+  </si>
+  <si>
+    <t>2SJ_Frequency_VFD</t>
+  </si>
+  <si>
+    <t>TI641aBM</t>
+  </si>
+  <si>
+    <t>Độ mở quạt gió #3</t>
+  </si>
+  <si>
+    <t>3_Blower_inlet_valve_location_1</t>
+  </si>
+  <si>
+    <t>Độ mở quạt gió #4</t>
+  </si>
+  <si>
+    <t>4_Blower_inlet_valve_location_1</t>
+  </si>
+  <si>
+    <t>TI601aBM</t>
+  </si>
+  <si>
+    <t>PI601aBM</t>
+  </si>
+  <si>
+    <t>TI601bBM</t>
+  </si>
+  <si>
+    <t>PI601bBM</t>
+  </si>
+  <si>
+    <t>TI602aBM</t>
+  </si>
+  <si>
+    <t>PI602aBM</t>
+  </si>
+  <si>
+    <t>TI602bBM</t>
+  </si>
+  <si>
+    <t>PI602bBM</t>
+  </si>
+  <si>
+    <t>TI603aBM</t>
+  </si>
+  <si>
+    <t>PI603aBM</t>
+  </si>
+  <si>
+    <t>TI603bBM</t>
+  </si>
+  <si>
+    <t>PI603bBM</t>
+  </si>
+  <si>
+    <t>TI614aBM</t>
+  </si>
+  <si>
+    <t>PI614aBM</t>
+  </si>
+  <si>
+    <t>TI614bBM</t>
+  </si>
+  <si>
+    <t>PI614bBM</t>
+  </si>
+  <si>
+    <t>TI615aBM</t>
+  </si>
+  <si>
+    <t>PI615aBM</t>
+  </si>
+  <si>
+    <t>TI615bBM</t>
+  </si>
+  <si>
+    <t>PI615bBM</t>
+  </si>
+  <si>
+    <t>TI616aBM</t>
+  </si>
+  <si>
+    <t>PI616aBM</t>
+  </si>
+  <si>
+    <t>Ống gió chính # 3</t>
+  </si>
+  <si>
+    <t>TI616bBM</t>
+  </si>
+  <si>
+    <t>Ống gió chính # 4</t>
+  </si>
+  <si>
+    <t>PI616bBM</t>
+  </si>
+  <si>
+    <t>TI617aBM</t>
+  </si>
+  <si>
+    <t>PI617aBM</t>
+  </si>
+  <si>
+    <t>TI617bBM</t>
+  </si>
+  <si>
+    <t>PI617bBM</t>
+  </si>
+  <si>
+    <t>TI618aBM</t>
+  </si>
+  <si>
+    <t>PI618aBM</t>
+  </si>
+  <si>
+    <t>TI618bBM</t>
+  </si>
+  <si>
+    <t>PI618bBM</t>
+  </si>
+  <si>
+    <t>TI619aBM</t>
+  </si>
+  <si>
+    <t>PI619aBM</t>
+  </si>
+  <si>
+    <t>TI619bBM</t>
+  </si>
+  <si>
+    <t>PI619bBM</t>
+  </si>
+  <si>
+    <t>TI620aBM</t>
+  </si>
+  <si>
+    <t>PI620aBM</t>
+  </si>
+  <si>
+    <t>TI620bBM</t>
+  </si>
+  <si>
+    <t>PI620bBM</t>
+  </si>
+  <si>
+    <t>TI621aBM</t>
+  </si>
+  <si>
+    <t>PI621aBM</t>
+  </si>
+  <si>
+    <t>TI621bBM</t>
+  </si>
+  <si>
+    <t>PI621bBM</t>
+  </si>
+  <si>
+    <t>TI636bBM</t>
+  </si>
+  <si>
+    <t>PI801bBM</t>
+  </si>
+  <si>
+    <t>TI636aBM</t>
+  </si>
+  <si>
+    <t>PI801aBM</t>
+  </si>
+  <si>
+    <t>LI601eBM</t>
   </si>
 </sst>
 </file>
@@ -1688,4 +1863,733 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228D5CF6-810E-488C-A06A-A79A11E9367B}">
+  <dimension ref="A1:D58"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+      <c r="B33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+      <c r="B34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+      <c r="B36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+      <c r="B37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+      <c r="B38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+      <c r="B39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+      <c r="B40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+      <c r="B41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+      <c r="B42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
+      <c r="B43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+      <c r="B44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
+      <c r="B45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+      <c r="B46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+      <c r="B47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+      <c r="B48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+      <c r="B49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+      <c r="B50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+      <c r="B51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+      <c r="B52" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+      <c r="B53" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="5"/>
+      <c r="B55" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="5"/>
+      <c r="B56" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="5"/>
+      <c r="B57" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A29"/>
+    <mergeCell ref="A30:A53"/>
+    <mergeCell ref="A54:A58"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/TagThieuKet.xlsx
+++ b/public/TagThieuKet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C091E6-7ADB-4214-9C2A-9C38FD540F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE3FDF-5762-4866-99F9-E42DE6E2EB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3720" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="TK1" sheetId="6" r:id="rId1"/>
@@ -523,157 +523,157 @@
     <t>4_Blower_inlet_valve_location_1</t>
   </si>
   <si>
+    <t>Ống gió chính # 3</t>
+  </si>
+  <si>
+    <t>Ống gió chính # 4</t>
+  </si>
+  <si>
+    <t>LI601eBM</t>
+  </si>
+  <si>
     <t>TI601aBM</t>
   </si>
   <si>
+    <t>TI601bBM</t>
+  </si>
+  <si>
+    <t>TI602aBM</t>
+  </si>
+  <si>
+    <t>TI602bBM</t>
+  </si>
+  <si>
+    <t>TI603aBM</t>
+  </si>
+  <si>
+    <t>TI603bBM</t>
+  </si>
+  <si>
+    <t>TI614aBM</t>
+  </si>
+  <si>
+    <t>TI614bBM</t>
+  </si>
+  <si>
+    <t>TI615aBM</t>
+  </si>
+  <si>
+    <t>TI615bBM</t>
+  </si>
+  <si>
+    <t>TI616aBM</t>
+  </si>
+  <si>
+    <t>TI616bBM</t>
+  </si>
+  <si>
+    <t>TI617aBM</t>
+  </si>
+  <si>
+    <t>TI617bBM</t>
+  </si>
+  <si>
+    <t>TI618aBM</t>
+  </si>
+  <si>
+    <t>TI618bBM</t>
+  </si>
+  <si>
+    <t>TI619aBM</t>
+  </si>
+  <si>
+    <t>TI619bBM</t>
+  </si>
+  <si>
+    <t>TI620aBM</t>
+  </si>
+  <si>
+    <t>TI620bBM</t>
+  </si>
+  <si>
+    <t>TI621aBM</t>
+  </si>
+  <si>
+    <t>TI621bBM</t>
+  </si>
+  <si>
+    <t>TI636bBM</t>
+  </si>
+  <si>
+    <t>TI636aBM</t>
+  </si>
+  <si>
     <t>PI601aBM</t>
   </si>
   <si>
-    <t>TI601bBM</t>
-  </si>
-  <si>
     <t>PI601bBM</t>
   </si>
   <si>
-    <t>TI602aBM</t>
-  </si>
-  <si>
     <t>PI602aBM</t>
   </si>
   <si>
-    <t>TI602bBM</t>
-  </si>
-  <si>
     <t>PI602bBM</t>
   </si>
   <si>
-    <t>TI603aBM</t>
-  </si>
-  <si>
     <t>PI603aBM</t>
   </si>
   <si>
-    <t>TI603bBM</t>
-  </si>
-  <si>
     <t>PI603bBM</t>
   </si>
   <si>
-    <t>TI614aBM</t>
-  </si>
-  <si>
     <t>PI614aBM</t>
   </si>
   <si>
-    <t>TI614bBM</t>
-  </si>
-  <si>
     <t>PI614bBM</t>
   </si>
   <si>
-    <t>TI615aBM</t>
-  </si>
-  <si>
     <t>PI615aBM</t>
   </si>
   <si>
-    <t>TI615bBM</t>
-  </si>
-  <si>
     <t>PI615bBM</t>
   </si>
   <si>
-    <t>TI616aBM</t>
-  </si>
-  <si>
     <t>PI616aBM</t>
   </si>
   <si>
-    <t>Ống gió chính # 3</t>
-  </si>
-  <si>
-    <t>TI616bBM</t>
-  </si>
-  <si>
-    <t>Ống gió chính # 4</t>
-  </si>
-  <si>
     <t>PI616bBM</t>
   </si>
   <si>
-    <t>TI617aBM</t>
-  </si>
-  <si>
     <t>PI617aBM</t>
   </si>
   <si>
-    <t>TI617bBM</t>
-  </si>
-  <si>
     <t>PI617bBM</t>
   </si>
   <si>
-    <t>TI618aBM</t>
-  </si>
-  <si>
     <t>PI618aBM</t>
   </si>
   <si>
-    <t>TI618bBM</t>
-  </si>
-  <si>
     <t>PI618bBM</t>
   </si>
   <si>
-    <t>TI619aBM</t>
-  </si>
-  <si>
     <t>PI619aBM</t>
   </si>
   <si>
-    <t>TI619bBM</t>
-  </si>
-  <si>
     <t>PI619bBM</t>
   </si>
   <si>
-    <t>TI620aBM</t>
-  </si>
-  <si>
     <t>PI620aBM</t>
   </si>
   <si>
-    <t>TI620bBM</t>
-  </si>
-  <si>
     <t>PI620bBM</t>
   </si>
   <si>
-    <t>TI621aBM</t>
-  </si>
-  <si>
     <t>PI621aBM</t>
   </si>
   <si>
-    <t>TI621bBM</t>
-  </si>
-  <si>
     <t>PI621bBM</t>
   </si>
   <si>
-    <t>TI636bBM</t>
-  </si>
-  <si>
     <t>PI801bBM</t>
   </si>
   <si>
-    <t>TI636aBM</t>
-  </si>
-  <si>
     <t>PI801aBM</t>
-  </si>
-  <si>
-    <t>LI601eBM</t>
   </si>
 </sst>
 </file>
@@ -1142,6 +1142,8 @@
     <col min="1" max="1" width="24.5703125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1231,7 +1233,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1243,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,7 +1257,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,7 +1269,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,7 +1293,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,7 +1305,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,7 +1317,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1327,7 +1329,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,7 +1341,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,7 +1353,7 @@
         <v>17</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,7 +1365,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,7 +1377,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,7 +1389,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1399,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1411,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,7 +1425,7 @@
         <v>23</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,7 +1437,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1447,7 +1449,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1459,7 +1461,7 @@
         <v>26</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,7 +1473,7 @@
         <v>27</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1483,7 +1485,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1495,7 +1497,7 @@
         <v>29</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1509,7 +1511,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1521,7 +1523,7 @@
         <v>61</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,7 +1535,7 @@
         <v>62</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1545,7 +1547,7 @@
         <v>63</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1557,7 +1559,7 @@
         <v>64</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,7 +1571,7 @@
         <v>120</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,7 +1583,7 @@
         <v>121</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1593,7 +1595,7 @@
         <v>122</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,7 +1607,7 @@
         <v>123</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,7 +1619,7 @@
         <v>124</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,7 +1631,7 @@
         <v>125</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1641,7 +1643,7 @@
         <v>126</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,7 +1655,7 @@
         <v>127</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1665,7 +1667,7 @@
         <v>128</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,7 +1679,7 @@
         <v>129</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1689,7 +1691,7 @@
         <v>130</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1701,7 +1703,7 @@
         <v>131</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1713,7 +1715,7 @@
         <v>132</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,7 +1727,7 @@
         <v>133</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1737,7 +1739,7 @@
         <v>134</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1749,7 +1751,7 @@
         <v>135</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1761,7 +1763,7 @@
         <v>136</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1773,7 +1775,7 @@
         <v>137</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,8 +1951,8 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>162</v>
+      <c r="D6" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,8 +1963,8 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>163</v>
+      <c r="D7" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1973,8 +1975,8 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>164</v>
+      <c r="D8" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1985,8 +1987,8 @@
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>165</v>
+      <c r="D9" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1997,8 +1999,8 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>166</v>
+      <c r="D10" s="3" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2009,8 +2011,8 @@
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>167</v>
+      <c r="D11" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2021,8 +2023,8 @@
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>168</v>
+      <c r="D12" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2033,8 +2035,8 @@
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>169</v>
+      <c r="D13" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2045,8 +2047,8 @@
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>170</v>
+      <c r="D14" s="3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2057,8 +2059,8 @@
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>171</v>
+      <c r="D15" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2069,8 +2071,8 @@
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>172</v>
+      <c r="D16" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2081,8 +2083,8 @@
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>173</v>
+      <c r="D17" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2093,8 +2095,8 @@
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>174</v>
+      <c r="D18" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2105,8 +2107,8 @@
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>175</v>
+      <c r="D19" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2117,8 +2119,8 @@
       <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>176</v>
+      <c r="D20" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2129,8 +2131,8 @@
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>177</v>
+      <c r="D21" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2141,8 +2143,8 @@
       <c r="C22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>178</v>
+      <c r="D22" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2153,8 +2155,8 @@
       <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>179</v>
+      <c r="D23" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2165,8 +2167,8 @@
       <c r="C24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>180</v>
+      <c r="D24" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2177,8 +2179,8 @@
       <c r="C25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>181</v>
+      <c r="D25" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2189,8 +2191,8 @@
       <c r="C26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>182</v>
+      <c r="D26" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,32 +2203,32 @@
       <c r="C27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>183</v>
+      <c r="D27" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="1" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>185</v>
+      <c r="D28" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="1" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>187</v>
+      <c r="D29" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2239,8 +2241,8 @@
       <c r="C30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>188</v>
+      <c r="D30" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2251,8 +2253,8 @@
       <c r="C31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>189</v>
+      <c r="D31" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2263,8 +2265,8 @@
       <c r="C32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>190</v>
+      <c r="D32" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2275,8 +2277,8 @@
       <c r="C33" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>191</v>
+      <c r="D33" s="3" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,8 +2289,8 @@
       <c r="C34" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>192</v>
+      <c r="D34" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2299,8 +2301,8 @@
       <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>193</v>
+      <c r="D35" s="3" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2311,8 +2313,8 @@
       <c r="C36" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>194</v>
+      <c r="D36" s="3" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2323,8 +2325,8 @@
       <c r="C37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>195</v>
+      <c r="D37" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2335,8 +2337,8 @@
       <c r="C38" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>196</v>
+      <c r="D38" s="3" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,8 +2349,8 @@
       <c r="C39" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>197</v>
+      <c r="D39" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2359,8 +2361,8 @@
       <c r="C40" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>198</v>
+      <c r="D40" s="3" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,8 +2373,8 @@
       <c r="C41" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>199</v>
+      <c r="D41" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2383,8 +2385,8 @@
       <c r="C42" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>200</v>
+      <c r="D42" s="3" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2395,8 +2397,8 @@
       <c r="C43" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>201</v>
+      <c r="D43" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2407,8 +2409,8 @@
       <c r="C44" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>202</v>
+      <c r="D44" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2419,8 +2421,8 @@
       <c r="C45" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>203</v>
+      <c r="D45" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2431,8 +2433,8 @@
       <c r="C46" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>204</v>
+      <c r="D46" s="3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2443,8 +2445,8 @@
       <c r="C47" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>205</v>
+      <c r="D47" s="3" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2455,8 +2457,8 @@
       <c r="C48" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>206</v>
+      <c r="D48" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2467,8 +2469,8 @@
       <c r="C49" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>207</v>
+      <c r="D49" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2479,8 +2481,8 @@
       <c r="C50" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>208</v>
+      <c r="D50" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2491,32 +2493,32 @@
       <c r="C51" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>209</v>
+      <c r="D51" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="1" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>210</v>
+      <c r="D52" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
       <c r="B53" s="1" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>211</v>
+      <c r="D53" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2578,17 +2580,17 @@
         <v>149</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A54:A58"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A29"/>
     <mergeCell ref="A30:A53"/>
-    <mergeCell ref="A54:A58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
